--- a/te_algorithms/data/summary_table_ld_sdg.xlsx
+++ b/te_algorithms/data/summary_table_ld_sdg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\azvoleff\Code\LandDegradation\trends.earth-prais-prep\docker\summary_worker\trends.earth-algorithms\te_algorithms\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-26.04\home\azvoleff\Code\LandDegradation\trends.earth-algorithms\te_algorithms\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DB8B43-9971-412E-949D-F3A55BF60EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC8682-6E17-44C1-9821-AF320EEA501E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="5145" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SDG 15.3.1" sheetId="5" r:id="rId1"/>
@@ -703,7 +703,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -796,6 +796,169 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -803,264 +966,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1094,9 +1004,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1134,7 +1044,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1240,7 +1150,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1382,7 +1292,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1393,13 +1303,11 @@
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="34"/>
-    <col min="2" max="2" width="14.5703125" style="34" customWidth="1"/>
-    <col min="3" max="5" width="15.5703125" style="35" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="35" customWidth="1"/>
-    <col min="7" max="9" width="15.5703125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="36" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="34"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="5" width="15.5703125" style="34" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="34" customWidth="1"/>
+    <col min="7" max="9" width="15.5703125" style="34" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -1420,44 +1328,44 @@
       <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-    </row>
-    <row r="4" spans="1:10" s="39" customFormat="1" ht="30.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="41"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="46" t="s">
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+    </row>
+    <row r="4" spans="1:10" s="36" customFormat="1" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="E5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="41">
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="47" t="e">
+      <c r="G5" s="44" t="e">
         <f>SUM(G6:G9)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1467,65 +1375,61 @@
       <c r="E6" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="e">
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="e">
         <f>F6/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="E7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="29" t="e">
         <f t="shared" ref="G7:G9" si="0">F7/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="40"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="E8" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56" t="e">
+      <c r="F8" s="49"/>
+      <c r="G8" s="50" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="E9" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54" t="e">
+      <c r="F9" s="47"/>
+      <c r="G9" s="48" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="40"/>
     </row>
     <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:10" s="37" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121" t="s">
+    <row r="11" spans="1:10" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="121"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
@@ -1547,41 +1451,56 @@
   <dimension ref="A1:J83"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="34" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="34" customWidth="1"/>
-    <col min="3" max="9" width="15.5703125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="36" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="34"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="9" width="15.5703125" style="34" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="50" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="50" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" s="50" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" ht="30.75" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="43" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1590,11 +1509,11 @@
       <c r="E5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="41">
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="47" t="e">
+      <c r="G5" s="44" t="e">
         <f>SUM(G6:G9)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1604,8 +1523,8 @@
       <c r="E6" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="e">
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="e">
         <f>F6/$F$5</f>
         <v>#DIV/0!</v>
       </c>
@@ -1615,7 +1534,7 @@
       <c r="E7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="29" t="e">
         <f t="shared" ref="G7:G9" si="0">F7/$F$5</f>
         <v>#DIV/0!</v>
@@ -1626,8 +1545,8 @@
       <c r="E8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56" t="e">
+      <c r="F8" s="49"/>
+      <c r="G8" s="50" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -1637,74 +1556,55 @@
       <c r="E9" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54" t="e">
+      <c r="F9" s="47"/>
+      <c r="G9" s="48" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="50" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
-    </row>
-    <row r="11" spans="1:10" s="50" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="124"/>
-    </row>
-    <row r="12" spans="1:10" s="50" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="82"/>
-    </row>
-    <row r="13" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="102" t="s">
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="91"/>
+    </row>
+    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-    </row>
-    <row r="14" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+    </row>
+    <row r="14" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="87"/>
+      <c r="J14" s="35"/>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="80"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="54" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="14" t="s">
@@ -1725,15 +1625,15 @@
       <c r="I15" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="82" t="s">
+      <c r="J15" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="23"/>
@@ -1749,7 +1649,6 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
       <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
@@ -1766,7 +1665,6 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
       <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1783,7 +1681,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1800,7 +1697,6 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83"/>
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1817,7 +1713,6 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83"/>
       <c r="B21" s="2" t="s">
         <v>39</v>
       </c>
@@ -1834,7 +1729,6 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="83"/>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
@@ -1888,41 +1782,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="80"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="82"/>
-    </row>
-    <row r="25" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="101" t="s">
+    <row r="25" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-    </row>
-    <row r="26" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="88" t="s">
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+    </row>
+    <row r="26" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J26" s="87"/>
+      <c r="J26" s="35"/>
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="80"/>
-      <c r="C27" s="59" t="s">
+      <c r="C27" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -1943,15 +1824,15 @@
       <c r="I27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="82" t="s">
+      <c r="J27" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84" t="s">
+      <c r="A28" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="23"/>
@@ -1967,7 +1848,6 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83"/>
       <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
@@ -1984,7 +1864,6 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="83"/>
       <c r="B30" s="2" t="s">
         <v>5</v>
       </c>
@@ -2001,7 +1880,6 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
       <c r="B31" s="2" t="s">
         <v>6</v>
       </c>
@@ -2018,7 +1896,6 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="83"/>
       <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
@@ -2035,7 +1912,6 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="83"/>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
@@ -2052,7 +1928,6 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="83"/>
       <c r="B34" s="2" t="s">
         <v>8</v>
       </c>
@@ -2106,45 +1981,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="80"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="82"/>
-    </row>
-    <row r="37" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="98" t="s">
+    <row r="37" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="100"/>
-    </row>
-    <row r="38" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="70"/>
+    </row>
+    <row r="38" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1"/>
-      <c r="C38" s="88" t="s">
+      <c r="C38" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J38" s="87"/>
+      <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="80" t="s">
+      <c r="A39" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="80"/>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -2165,15 +2027,15 @@
       <c r="I39" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="82" t="s">
+      <c r="J39" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="23"/>
@@ -2189,7 +2051,6 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
       <c r="B41" s="2" t="s">
         <v>4</v>
       </c>
@@ -2206,7 +2067,6 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
       <c r="B42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2223,7 +2083,6 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
       <c r="B43" s="2" t="s">
         <v>6</v>
       </c>
@@ -2240,7 +2099,6 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
       <c r="B44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2257,7 +2115,6 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="83"/>
       <c r="B45" s="2" t="s">
         <v>39</v>
       </c>
@@ -2274,7 +2131,6 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="83"/>
       <c r="B46" s="2" t="s">
         <v>8</v>
       </c>
@@ -2328,43 +2184,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="80"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="82"/>
-    </row>
-    <row r="49" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="95" t="s">
+    <row r="49" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="96"/>
-      <c r="C49" s="96"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="96"/>
-      <c r="H49" s="96"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="97"/>
-    </row>
-    <row r="50" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="67"/>
+    </row>
+    <row r="50" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
-      <c r="C50" s="88" t="s">
+      <c r="C50" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J50" s="87"/>
+      <c r="J50" s="35"/>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="80"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="59" t="s">
+      <c r="C51" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -2385,15 +2227,15 @@
       <c r="I51" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="82" t="s">
+      <c r="J51" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="84" t="s">
+      <c r="A52" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="23"/>
@@ -2409,7 +2251,6 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="83"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
@@ -2426,7 +2267,6 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="83"/>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
@@ -2443,7 +2283,6 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="83"/>
       <c r="B55" s="2" t="s">
         <v>6</v>
       </c>
@@ -2460,7 +2299,6 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="83"/>
       <c r="B56" s="2" t="s">
         <v>7</v>
       </c>
@@ -2477,7 +2315,6 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="83"/>
       <c r="B57" s="2" t="s">
         <v>39</v>
       </c>
@@ -2494,7 +2331,6 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="83"/>
       <c r="B58" s="2" t="s">
         <v>8</v>
       </c>
@@ -2548,43 +2384,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="80"/>
-      <c r="B60" s="80"/>
-      <c r="C60" s="81"/>
-      <c r="D60" s="81"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="81"/>
-      <c r="I60" s="81"/>
-      <c r="J60" s="82"/>
-    </row>
-    <row r="61" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92" t="s">
+    <row r="61" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="93"/>
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="93"/>
-      <c r="F61" s="93"/>
-      <c r="G61" s="93"/>
-      <c r="H61" s="93"/>
-      <c r="I61" s="93"/>
-      <c r="J61" s="94"/>
-    </row>
-    <row r="62" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="64"/>
+    </row>
+    <row r="62" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
-      <c r="C62" s="88" t="s">
+      <c r="C62" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J62" s="87"/>
-    </row>
-    <row r="63" spans="1:10" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="80"/>
-      <c r="B63" s="80"/>
-      <c r="C63" s="59" t="s">
+      <c r="J62" s="35"/>
+    </row>
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="C63" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -2605,15 +2427,15 @@
       <c r="I63" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="82" t="s">
+      <c r="J63" s="35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="50" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="84" t="s">
+    <row r="64" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="23"/>
@@ -2628,8 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="83"/>
+    <row r="65" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>4</v>
       </c>
@@ -2645,8 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="83"/>
+    <row r="66" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>5</v>
       </c>
@@ -2662,8 +2482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="83"/>
+    <row r="67" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>6</v>
       </c>
@@ -2679,8 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="83"/>
+    <row r="68" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>7</v>
       </c>
@@ -2696,8 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="83"/>
+    <row r="69" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>39</v>
       </c>
@@ -2713,8 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="83"/>
+    <row r="70" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
@@ -2730,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
         <v>9</v>
@@ -2768,43 +2584,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="80"/>
-      <c r="B72" s="80"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="81"/>
-      <c r="E72" s="81"/>
-      <c r="F72" s="81"/>
-      <c r="G72" s="81"/>
-      <c r="H72" s="81"/>
-      <c r="I72" s="81"/>
-      <c r="J72" s="82"/>
-    </row>
-    <row r="73" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="89" t="s">
+    <row r="73" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="B73" s="90"/>
-      <c r="C73" s="90"/>
-      <c r="D73" s="90"/>
-      <c r="E73" s="90"/>
-      <c r="F73" s="90"/>
-      <c r="G73" s="90"/>
-      <c r="H73" s="90"/>
-      <c r="I73" s="90"/>
-      <c r="J73" s="91"/>
-    </row>
-    <row r="74" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="61"/>
+    </row>
+    <row r="74" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="1"/>
-      <c r="C74" s="88" t="s">
+      <c r="C74" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J74" s="87"/>
-    </row>
-    <row r="75" spans="1:10" s="50" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
-      <c r="B75" s="80"/>
-      <c r="C75" s="59" t="s">
+      <c r="J74" s="35"/>
+    </row>
+    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="C75" s="53" t="s">
         <v>16</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -2825,15 +2627,15 @@
       <c r="I75" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="82" t="s">
+      <c r="J75" s="35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:10" s="50" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="84" t="s">
+    <row r="76" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="23"/>
@@ -2848,8 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="83"/>
+    <row r="77" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
         <v>4</v>
       </c>
@@ -2865,8 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="83"/>
+    <row r="78" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
         <v>5</v>
       </c>
@@ -2882,8 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="83"/>
+    <row r="79" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
         <v>6</v>
       </c>
@@ -2899,8 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="83"/>
+    <row r="80" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
         <v>7</v>
       </c>
@@ -2916,8 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="83"/>
+    <row r="81" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="2" t="s">
         <v>39</v>
       </c>
@@ -2933,8 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="83"/>
+    <row r="82" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
         <v>8</v>
       </c>
@@ -2950,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="50" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="6" t="s">
         <v>9</v>
@@ -3003,10 +2799,8 @@
   <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="34"/>
-    <col min="2" max="2" width="14.5703125" style="34" customWidth="1"/>
-    <col min="3" max="10" width="15.5703125" style="34" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="34"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="10" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3018,110 +2812,110 @@
       <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" ht="30.75" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="43" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="41">
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="47" t="e">
+      <c r="G5" s="44" t="e">
         <f>SUM(G6:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="e">
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="e">
         <f>F6/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="29" t="e">
         <f t="shared" ref="G7:G9" si="0">F7/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56" t="e">
+      <c r="F8" s="49"/>
+      <c r="G8" s="50" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="35"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54" t="e">
+      <c r="F9" s="47"/>
+      <c r="G9" s="48" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
@@ -3140,25 +2934,23 @@
       <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="110" t="s">
+      <c r="A13" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
     </row>
     <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
-      <c r="B15" s="108"/>
       <c r="C15" s="17" t="s">
         <v>57</v>
       </c>
@@ -3174,12 +2966,10 @@
       <c r="G15" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
     </row>
     <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="113"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="79"/>
+      <c r="B16" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="26" t="e">
@@ -3193,11 +2983,8 @@
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-    </row>
-    <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83"/>
+    </row>
+    <row r="17" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
@@ -3212,11 +2999,8 @@
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
       <c r="G17" s="26"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-    </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
+    </row>
+    <row r="18" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
@@ -3231,11 +3015,8 @@
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
       <c r="G18" s="26"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="108"/>
-    </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
+    </row>
+    <row r="19" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
@@ -3250,11 +3031,8 @@
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-    </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="83"/>
+    </row>
+    <row r="20" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>7</v>
       </c>
@@ -3269,11 +3047,8 @@
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
       <c r="G20" s="26"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="108"/>
-    </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="83"/>
+    </row>
+    <row r="21" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>39</v>
       </c>
@@ -3288,12 +3063,9 @@
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="108"/>
-    </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="108"/>
       <c r="C22" s="25"/>
       <c r="D22" s="6" t="s">
         <v>9</v>
@@ -3310,34 +3082,20 @@
         <f>SUM(G16:G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="108"/>
-      <c r="I22" s="108"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="108"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="108"/>
-    </row>
-    <row r="24" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="103" t="s">
+    </row>
+    <row r="24" spans="1:9" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="73" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="56" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="108"/>
-      <c r="B26" s="81"/>
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="34"/>
       <c r="C26" s="32" t="s">
         <v>16</v>
       </c>
@@ -3356,120 +3114,99 @@
       <c r="H26" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I26" s="114"/>
-      <c r="J26" s="115"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86" t="s">
+      <c r="I26" s="34"/>
+    </row>
+    <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="105" t="s">
+      <c r="B27" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="119"/>
-      <c r="J27" s="115"/>
-    </row>
-    <row r="28" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83"/>
-      <c r="B28" s="107" t="s">
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="81"/>
+    </row>
+    <row r="28" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="119"/>
-      <c r="J28" s="115"/>
-    </row>
-    <row r="29" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83"/>
-      <c r="B29" s="107" t="s">
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="81"/>
+    </row>
+    <row r="29" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="115"/>
-    </row>
-    <row r="30" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="83"/>
-      <c r="B30" s="107" t="s">
+      <c r="C29" s="76"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="81"/>
+    </row>
+    <row r="30" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="115"/>
-    </row>
-    <row r="31" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
-      <c r="B31" s="107" t="s">
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="81"/>
+    </row>
+    <row r="31" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="119"/>
-      <c r="J31" s="115"/>
-    </row>
-    <row r="32" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="83"/>
-      <c r="B32" s="107" t="s">
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="81"/>
+    </row>
+    <row r="32" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="106"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="119"/>
-      <c r="J32" s="115"/>
-    </row>
-    <row r="33" spans="1:10" s="38" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="81"/>
+    </row>
+    <row r="33" spans="1:10" s="37" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
-      <c r="B33" s="111"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-    </row>
-    <row r="34" spans="1:10" s="38" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="109" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+    </row>
+    <row r="34" spans="1:10" s="37" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="112"/>
-      <c r="C34" s="112"/>
-      <c r="D34" s="112"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="112"/>
-      <c r="G34" s="112"/>
-      <c r="H34" s="112"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3485,11 +3222,10 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="34" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="34" customWidth="1"/>
-    <col min="3" max="9" width="15.5703125" style="34" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="36" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="34"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3502,131 +3238,129 @@
       <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="124"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10" ht="30.75" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="43" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="E5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="41">
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="47" t="e">
+      <c r="G5" s="44" t="e">
         <f>SUM(G6:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52" t="e">
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="e">
         <f>F6/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="42"/>
       <c r="G7" s="29" t="e">
         <f t="shared" ref="G7:G9" si="0">F7/$F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56" t="e">
+      <c r="F8" s="49"/>
+      <c r="G8" s="50" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54" t="e">
+      <c r="F9" s="47"/>
+      <c r="G9" s="48" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="J10" s="34"/>
+      <c r="J10"/>
     </row>
     <row r="11" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="125" t="s">
+      <c r="A11" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="126"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="J12" s="34"/>
+      <c r="J12"/>
     </row>
     <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="108"/>
-      <c r="B13" s="108"/>
       <c r="C13" s="17" t="s">
         <v>58</v>
       </c>
@@ -3639,14 +3373,10 @@
       <c r="F13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="111"/>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="113"/>
-      <c r="B14" s="57" t="s">
+      <c r="A14" s="79"/>
+      <c r="B14" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="23">
@@ -3665,13 +3395,9 @@
         <f t="shared" ref="F14:F20" si="3">(D14-C14)/C14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G14" s="108"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="111"/>
     </row>
     <row r="15" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="113"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="2" t="s">
         <v>4</v>
       </c>
@@ -3691,13 +3417,9 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="111"/>
     </row>
     <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="113"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
@@ -3717,13 +3439,9 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="111"/>
     </row>
     <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="113"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
@@ -3743,13 +3461,9 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="108"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="111"/>
     </row>
     <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="113"/>
+      <c r="A18" s="79"/>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
@@ -3769,13 +3483,9 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="108"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="111"/>
     </row>
     <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="113"/>
+      <c r="A19" s="79"/>
       <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
@@ -3795,13 +3505,9 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="111"/>
     </row>
     <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="113"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
@@ -3821,10 +3527,6 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="108"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="111"/>
     </row>
     <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
@@ -3841,40 +3543,28 @@
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="22"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="111"/>
     </row>
     <row r="22" spans="1:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="6"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="111"/>
-    </row>
-    <row r="23" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="104" t="s">
+    </row>
+    <row r="23" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="111"/>
-    </row>
-    <row r="24" spans="1:10" s="81" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="35"/>
+    </row>
+    <row r="24" spans="1:10" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="J24" s="111"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="108"/>
-      <c r="B25" s="108"/>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="52" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="20" t="s">
@@ -3895,15 +3585,15 @@
       <c r="I25" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="111" t="s">
+      <c r="J25" s="35" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="51" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="23"/>
@@ -3919,7 +3609,6 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="83"/>
       <c r="B27" s="2" t="s">
         <v>4</v>
       </c>
@@ -3936,7 +3625,6 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="83"/>
       <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
@@ -3953,7 +3641,6 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83"/>
       <c r="B29" s="2" t="s">
         <v>6</v>
       </c>
@@ -3970,7 +3657,6 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="83"/>
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
@@ -3987,7 +3673,6 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
@@ -4004,7 +3689,6 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="83"/>
       <c r="B32" s="2" t="s">
         <v>8</v>
       </c>
@@ -4020,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="38" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="37" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
       <c r="B33" s="6" t="s">
         <v>9</v>
@@ -4082,176 +3766,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="66"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="63"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
+      <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="124"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="71" t="s">
+      <c r="A4" s="4"/>
+      <c r="D4" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="61" t="s">
+      <c r="E4" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="61" t="s">
+      <c r="G4" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="63"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="4"/>
+      <c r="C5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="41">
         <f>'SDG 15.3.1'!F5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="75" t="e">
+      <c r="E5" s="44" t="e">
         <f>'SDG 15.3.1'!G5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F5" s="128">
+      <c r="F5" s="82">
         <f>SUM(F6:F9)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="75" t="e">
+      <c r="G5" s="44" t="e">
         <f>SUM(G6:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I5" s="68"/>
-      <c r="J5" s="62"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="63"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="67" t="s">
+      <c r="A6" s="4"/>
+      <c r="C6" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="45">
         <f>'SDG 15.3.1'!F6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="76" t="e">
+      <c r="E6" s="46" t="e">
         <f>'SDG 15.3.1'!G6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F6" s="129"/>
-      <c r="G6" s="76" t="e">
+      <c r="F6" s="83"/>
+      <c r="G6" s="46" t="e">
         <f>F6/F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I6" s="68"/>
-      <c r="J6" s="62"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="63"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="67" t="s">
+      <c r="A7" s="4"/>
+      <c r="C7" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="42">
+        <f>'SDG 15.3.1'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="29" t="e">
+        <f>'SDG 15.3.1'!G7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F7" s="84"/>
+      <c r="G7" s="29" t="e">
+        <f>F7/F$5</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="34"/>
+    </row>
+    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="C8" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="49">
         <f>'SDG 15.3.1'!F8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="77" t="e">
-        <f>'SDG 15.3.1'!G7</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="130"/>
-      <c r="G7" s="77" t="e">
-        <f>F7/F$5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I7" s="68"/>
-      <c r="J7" s="62"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="63"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="74">
-        <f>'SDG 15.3.1'!F8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="78" t="e">
+      <c r="E8" s="50" t="e">
         <f>'SDG 15.3.1'!G8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F8" s="131"/>
-      <c r="G8" s="78" t="e">
+      <c r="F8" s="85"/>
+      <c r="G8" s="50" t="e">
         <f>F8/F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I8" s="68"/>
-      <c r="J8" s="62"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="63"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="67" t="s">
+      <c r="A9" s="4"/>
+      <c r="C9" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="47">
         <f>'SDG 15.3.1'!F9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="79" t="e">
+      <c r="E9" s="48" t="e">
         <f>'SDG 15.3.1'!G9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F9" s="132"/>
-      <c r="G9" s="79" t="e">
+      <c r="F9" s="86"/>
+      <c r="G9" s="48" t="e">
         <f>F9/F$5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="68"/>
-      <c r="J9" s="62"/>
+      <c r="I9" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
